--- a/dist/checklists/xlsx/dwc/spatial_transcriptomics_image_manifest_version_dwc_stx_fish_v0.1.xlsx
+++ b/dist/checklists/xlsx/dwc/spatial_transcriptomics_image_manifest_version_dwc_stx_fish_v0.1.xlsx
@@ -877,7 +877,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection password="B9C8" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="D7A3" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -944,7 +944,7 @@
       <c r="D4" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection password="A524" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="E5FD" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:D4"/>
   </mergeCells>
@@ -4127,7 +4127,7 @@
       <c r="A1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="C87A" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="D488" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:H4"/>
   </mergeCells>
@@ -8217,7 +8217,7 @@
       <c r="B1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="BC6A" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="E77C" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:E4"/>
   </mergeCells>
@@ -12439,7 +12439,7 @@
       <c r="B1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="EDFE" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="ACEC" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:Q4"/>
   </mergeCells>
@@ -17535,7 +17535,7 @@
       <c r="C1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="86E8" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="C6F1" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:E4"/>
   </mergeCells>

--- a/dist/checklists/xlsx/dwc/spatial_transcriptomics_image_manifest_version_dwc_stx_fish_v0.1.xlsx
+++ b/dist/checklists/xlsx/dwc/spatial_transcriptomics_image_manifest_version_dwc_stx_fish_v0.1.xlsx
@@ -877,7 +877,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection password="D7A3" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="B8C2" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -944,7 +944,7 @@
       <c r="D4" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection password="E5FD" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="D870" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:D4"/>
   </mergeCells>
@@ -4127,7 +4127,7 @@
       <c r="A1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="D488" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="B789" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:H4"/>
   </mergeCells>
@@ -8217,7 +8217,7 @@
       <c r="B1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="E77C" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="B450" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:E4"/>
   </mergeCells>
@@ -12439,7 +12439,7 @@
       <c r="B1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="ACEC" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="8E49" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:Q4"/>
   </mergeCells>
@@ -17535,7 +17535,7 @@
       <c r="C1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="C6F1" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="93B2" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:E4"/>
   </mergeCells>

--- a/dist/checklists/xlsx/dwc/spatial_transcriptomics_image_manifest_version_dwc_stx_fish_v0.1.xlsx
+++ b/dist/checklists/xlsx/dwc/spatial_transcriptomics_image_manifest_version_dwc_stx_fish_v0.1.xlsx
@@ -877,7 +877,7 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection password="B8C2" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="AFC2" sheet="1" objects="1" scenarios="1"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -944,7 +944,7 @@
       <c r="D4" s="6"/>
     </row>
   </sheetData>
-  <sheetProtection password="D870" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="F4B7" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:D4"/>
   </mergeCells>
@@ -4127,7 +4127,7 @@
       <c r="A1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="B789" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="8976" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:H4"/>
   </mergeCells>
@@ -8217,7 +8217,7 @@
       <c r="B1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="B450" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="A84A" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:E4"/>
   </mergeCells>
@@ -12439,7 +12439,7 @@
       <c r="B1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="8E49" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="8855" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:Q4"/>
   </mergeCells>
@@ -17535,7 +17535,7 @@
       <c r="C1005" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection password="93B2" sheet="1" objects="1" scenarios="1"/>
+  <sheetProtection password="F763" sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="1">
     <mergeCell ref="A4:E4"/>
   </mergeCells>
